--- a/TNE20002 Scenario Calculator.xlsx
+++ b/TNE20002 Scenario Calculator.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\University\Network Routing Principles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E54EFDB7-3C85-4964-84CC-DFC583D4BA06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3734A520-1CD5-4A15-BA75-74D3327F9744}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3855" yWindow="3855" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29070" yWindow="3270" windowWidth="10995" windowHeight="10200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -137,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -147,6 +147,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -507,26 +511,26 @@
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B10" s="2">
+      <c r="B10" s="3">
         <v>1</v>
       </c>
-      <c r="C10" s="2" t="str">
+      <c r="C10" s="3" t="str">
         <f>CONCATENATE("158.",$J$11,$J$13,".0.0/16")</f>
         <v>158.72.0.0/16</v>
       </c>
-      <c r="D10" t="str">
+      <c r="D10" s="4" t="str">
         <f>CONCATENATE("201.24.4",$J$12,".0/30")</f>
         <v>201.24.41.0/30</v>
       </c>
-      <c r="E10" t="str">
+      <c r="E10" s="4" t="str">
         <f>CONCATENATE("VLAN",$L$7)</f>
         <v>VLAN712</v>
       </c>
-      <c r="F10" t="str">
+      <c r="F10" s="4" t="str">
         <f>CONCATENATE("VLAN",$L$6)</f>
         <v>VLAN928</v>
       </c>
-      <c r="G10" t="str">
+      <c r="G10" s="4" t="str">
         <f>CONCATENATE("VLAN",IF(OR($L$7="256",$L$6="256"),253,256))</f>
         <v>VLAN256</v>
       </c>
@@ -585,26 +589,26 @@
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B12" s="3">
+      <c r="B12" s="5">
         <v>3</v>
       </c>
-      <c r="C12" s="3" t="str">
+      <c r="C12" s="5" t="str">
         <f>CONCATENATE("131.",$J$11,$J$13,".0.0/17")</f>
         <v>131.72.0.0/17</v>
       </c>
-      <c r="D12" s="4" t="str">
+      <c r="D12" s="6" t="str">
         <f>CONCATENATE("211.13.8",$J$12,".0/30")</f>
         <v>211.13.81.0/30</v>
       </c>
-      <c r="E12" s="4" t="str">
+      <c r="E12" s="6" t="str">
         <f>CONCATENATE("VLAN",$L$7)</f>
         <v>VLAN712</v>
       </c>
-      <c r="F12" s="4" t="str">
+      <c r="F12" s="6" t="str">
         <f>CONCATENATE("VLAN",$L$6)</f>
         <v>VLAN928</v>
       </c>
-      <c r="G12" s="4" t="str">
+      <c r="G12" s="6" t="str">
         <f>CONCATENATE("VLAN",IF(OR($L$7="112",$L$6="112"),109,112))</f>
         <v>VLAN112</v>
       </c>
